--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF570F66-4213-40CF-AEB6-7881D866EE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC926A36-55DF-453F-915D-898BA20AA9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
   <si>
     <t>单片机矩阵键盘3*4</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -488,12 +488,16 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>图片仅供参考，请按照文字器件描述购买</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,6 +538,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -566,13 +579,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -820,8 +833,8 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>61953</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1711459</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>8963</xdr:rowOff>
     </xdr:to>
@@ -1631,8 +1644,8 @@
       <xdr:rowOff>7463</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>616558</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2266064</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>113454</xdr:rowOff>
     </xdr:to>
@@ -1692,8 +1705,8 @@
       <xdr:rowOff>48746</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>541020</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2190526</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>72116</xdr:rowOff>
     </xdr:to>
@@ -1936,8 +1949,8 @@
       <xdr:rowOff>48791</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>4773</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1654279</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>530087</xdr:rowOff>
     </xdr:to>
@@ -2546,8 +2559,8 @@
       <xdr:rowOff>107577</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>172123</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1821629</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>770338</xdr:rowOff>
     </xdr:to>
@@ -2872,7 +2885,7 @@
     <col min="2" max="2" width="39" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" customWidth="1"/>
     <col min="4" max="4" width="9.77734375" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" customWidth="1"/>
     <col min="6" max="6" width="59.88671875" customWidth="1"/>
     <col min="7" max="7" width="12.88671875" customWidth="1"/>
     <col min="9" max="9" width="8.33203125" customWidth="1"/>
@@ -2888,7 +2901,9 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
+      <c r="E1" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
@@ -2990,7 +3005,7 @@
       <c r="C10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>1</v>
       </c>
     </row>
@@ -3112,7 +3127,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+      <c r="A20" s="5"/>
       <c r="B20">
         <v>240</v>
       </c>

--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC926A36-55DF-453F-915D-898BA20AA9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D394F3E6-9705-433A-8A8F-C2A1A49594A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="114">
   <si>
     <t>单片机矩阵键盘3*4</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -490,6 +490,10 @@
   </si>
   <si>
     <t>图片仅供参考，请按照文字器件描述购买</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2923,7 +2927,9 @@
       <c r="B3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>

--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D394F3E6-9705-433A-8A8F-C2A1A49594A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8DC8DA-D8CD-40E5-9821-6D47AC071C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
   <si>
     <t>单片机矩阵键盘3*4</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -494,6 +494,10 @@
   </si>
   <si>
     <t>LCD1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST-link V2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -657,13 +661,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1349829</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>1112</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1057,13 +1061,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1234441</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>350520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>2034541</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>207230</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1101,13 +1105,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1389435</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>2533849</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>65931</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1145,13 +1149,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>2011680</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>408335</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2612,6 +2616,50 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>34578</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>331429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1354184</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>29477</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B8C073-913E-A848-9DED-F527370AF897}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7132064" y="21841600"/>
+          <a:ext cx="1319606" cy="547134"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2882,7 +2930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -3452,61 +3500,73 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="F47" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="48" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="F48" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="1"/>
+    </row>
+    <row r="49" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-    </row>
-    <row r="50" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="1"/>
+      <c r="F49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-    </row>
-    <row r="51" spans="2:5" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="2:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
+      <c r="C53" s="1"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="2:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="2:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
+    <row r="55" spans="2:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="2:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
+    <row r="56" spans="2:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8DC8DA-D8CD-40E5-9821-6D47AC071C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BF9721-2923-425D-9C1E-01E3EE0CF388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -416,10 +416,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>各类焊接工具：电烙铁、焊锡丝、热熔胶/胶枪等等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>银灰色PVC警示胶带 30mm宽度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -498,6 +494,10 @@
   </si>
   <si>
     <t>ST-link V2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各类焊接工具：电烙铁、焊锡丝、镊子、热熔胶/胶枪等等</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2954,7 +2954,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
@@ -2973,16 +2973,16 @@
     </row>
     <row r="3" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -3086,14 +3086,14 @@
     </row>
     <row r="13" spans="2:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -3375,7 +3375,7 @@
     </row>
     <row r="35" spans="2:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
         <v>44</v>
@@ -3442,7 +3442,7 @@
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -3481,12 +3481,12 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -3507,7 +3507,7 @@
     </row>
     <row r="47" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="53" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>

--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFA31F9-F836-4B0E-99EF-8BD950DD83C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9198EE75-A21A-4ABE-9370-0E2DF487653F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -155,10 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无源蜂鸣器4kHz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LED5mm 红绿双色 共阴极3脚</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -442,6 +438,38 @@
       </rPr>
       <t>不要买焊接好排针的版本</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片仅供参考，请按照文字器件描述购买</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST-link V2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各类焊接工具：电烙铁、焊锡丝、镊子、热熔胶/胶枪等等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R6 /LCD-R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贴片电阻240欧姆0805封装/ 注LCD转接板背面的R1需要焊接此电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1k-0805 / 这里的R1指的是主板上的R1，转接板上的R1请焊接240R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无源蜂鸣器4kHz 2-7V</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -468,36 +496,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>）</t>
+      <t>）5V</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图片仅供参考，请按照文字器件描述购买</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LCD1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ST-link V2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各类焊接工具：电烙铁、焊锡丝、镊子、热熔胶/胶枪等等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R6 /LCD-R1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贴片电阻240欧姆0805封装/ 注LCD转接板背面的R1需要焊接此电阻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1k-0805 / 这里的R1指的是主板上的R1，转接板上的R1请焊接240R</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2948,13 +2948,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
@@ -2965,7 +2965,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -2973,16 +2973,16 @@
     </row>
     <row r="3" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,10 @@
     </row>
     <row r="8" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="9" spans="2:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -3086,98 +3086,98 @@
     </row>
     <row r="13" spans="2:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
         <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
         <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>59</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -3186,13 +3186,13 @@
         <v>240</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3200,144 +3200,144 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
         <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
         <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
         <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>89</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
         <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>92</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
         <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>95</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="32" spans="1:6" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -3353,10 +3353,10 @@
     </row>
     <row r="33" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="34" spans="2:6" ht="47.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="35" spans="2:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="36" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
         <v>47</v>
-      </c>
-      <c r="C36" t="s">
-        <v>48</v>
       </c>
       <c r="D36" s="1">
         <v>4</v>
@@ -3397,44 +3397,44 @@
     </row>
     <row r="37" spans="2:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -3442,7 +3442,7 @@
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -3464,7 +3464,7 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3481,12 +3481,12 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -3507,7 +3507,7 @@
     </row>
     <row r="47" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="53" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>

--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9198EE75-A21A-4ABE-9370-0E2DF487653F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3DD5E3-B4AC-4C02-8968-7F317155D26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
   <si>
     <t>单片机矩阵键盘3*4</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -466,10 +466,6 @@
   </si>
   <si>
     <t>1k-0805 / 这里的R1指的是主板上的R1，转接板上的R1请焊接240R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无源蜂鸣器4kHz 2-7V</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -498,6 +494,14 @@
       </rPr>
       <t>）5V</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">无源蜂鸣器4kHz 5V </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>或者 2-7V，或者包含5V的就行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2973,7 +2977,7 @@
     </row>
     <row r="3" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>107</v>
@@ -3032,13 +3036,16 @@
     </row>
     <row r="8" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
